--- a/artfynd/A 21720-2026 artfynd.xlsx
+++ b/artfynd/A 21720-2026 artfynd.xlsx
@@ -675,45 +675,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134215435</v>
+        <v>134215440</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öster-näversjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468550</v>
+        <v>468464</v>
       </c>
       <c r="R2" t="n">
-        <v>7033823</v>
+        <v>7033855</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +762,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,61 +788,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134215440</v>
+        <v>134215435</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öster-näversjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468464</v>
+        <v>468550</v>
       </c>
       <c r="R3" t="n">
-        <v>7033855</v>
+        <v>7033823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,6 +859,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 21720-2026 artfynd.xlsx
+++ b/artfynd/A 21720-2026 artfynd.xlsx
@@ -675,61 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134215440</v>
+        <v>134215435</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öster-näversjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468464</v>
+        <v>468550</v>
       </c>
       <c r="R2" t="n">
-        <v>7033855</v>
+        <v>7033823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,45 +777,61 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134215435</v>
+        <v>134215440</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öster-näversjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468550</v>
+        <v>468464</v>
       </c>
       <c r="R3" t="n">
-        <v>7033823</v>
+        <v>7033855</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,11 +864,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 21720-2026 artfynd.xlsx
+++ b/artfynd/A 21720-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215435</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,8 +897,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215440</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>